--- a/TestData/TMTT0005211_RefreshButtonFunctionalities.xlsx
+++ b/TestData/TMTT0005211_RefreshButtonFunctionalities.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AECE4B1-5D80-437C-BCE8-71AA01AFDDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB3F942-2D48-4CD3-8D2B-49A232D8FA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
-    <sheet name="Time_Record_Period_Title" sheetId="9" r:id="rId2"/>
-    <sheet name="Update_Timer" sheetId="10" r:id="rId3"/>
-    <sheet name="Project_Title" sheetId="11" r:id="rId4"/>
+    <sheet name="AppName" sheetId="12" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="13" r:id="rId3"/>
+    <sheet name="Time_Record_Period_Title" sheetId="9" r:id="rId4"/>
+    <sheet name="Update_Timer" sheetId="10" r:id="rId5"/>
+    <sheet name="Project_Title" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,10 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Yuka Itami</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Global Search User</t>
   </si>
@@ -61,6 +60,33 @@
   </si>
   <si>
     <t>GE Healthcare-GE Healthcare Bio-Sciences AB-FVA-101397</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Amy Xia</t>
+  </si>
+  <si>
+    <t>Time Tracking Litigation</t>
+  </si>
+  <si>
+    <t>CF Financial User</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Time Record Manager</t>
   </si>
 </sst>
 </file>
@@ -287,7 +313,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -399,6 +425,21 @@
       </top>
       <bottom style="double">
         <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -443,13 +484,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -772,17 +814,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -791,18 +845,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6159055F-657C-469F-A844-980074572638}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87432E7-4596-40AF-9220-79A9A2ED8B29}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -811,19 +905,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -831,33 +925,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
